--- a/news_daily/2026-08-15.xlsx
+++ b/news_daily/2026-08-15.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -1684,28 +1684,32 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1749,7 +1753,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1758,7 +1762,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>d8e92859ce274410b810fbd447d69c27</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>bd91189dd528e4891b57bc3d</t>
@@ -1779,7 +1787,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1823,10 +1835,22 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2225,174 +2249,198 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2026-08-15T21:08:23+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Coinbase (COIN) Stock Still Looks Overvalued Despite New York Probe</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>估值疑慮</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>0.823</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxONzc5SFdHcTJZSm1BWmw3Tm1oeGlHaXdDclJYbnY0TFZVWmlfNjdYUjRmUFVOZ1ZZaXB0eHFrQWl2M01JNHR4YTI3LWJXYVl5WU1sTU9OYWNiaW40c1VYV3ZYdlZrRXFhUjhhMEpDQVN6S0xJa3FzbXhxRVlYenNzTW9vekxZLS1sRFVGazdIMk5Dd0VVZmhlUzVpOHk?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>儘管紐約調查，Coinbase (COIN) 股票看起來仍然被高估</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>overvalued</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>186e905bd4d743c7bd79ec88b35d11f8</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>3b2b8a529ce20d3abdfd51d2</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>6c89cb0cd0f4131e12a66479</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr"/>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>0.823</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxONzc5SFdHcTJZSm1BWmw3Tm1oeGlHaXdDclJYbnY0TFZVWmlfNjdYUjRmUFVOZ1ZZaXB0eHFrQWl2M01JNHR4YTI3LWJXYVl5WU1sTU9OYWNiaW40c1VYV3ZYdlZrRXFhUjhhMEpDQVN6S0xJa3FzbXhxRVlYenNzTW9vekxZLS1sRFVGazdIMk5Dd0VVZmhlUzVpOHk?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>儘管紐約調查，Coinbase (COIN) 股票看起來仍然被高估</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>VALUATION_CONCERN</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>overvalued</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>3b2b8a529ce20d3abdfd51d2</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>6c89cb0cd0f4131e12a66479</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr"/>
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BF9" s="4" t="inlineStr"/>
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3037,13 +3085,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3096,7 +3148,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>2166b14c67ef439cb60c91fb1b228f74</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>4445d369023095efb8adec2b</t>
@@ -3117,7 +3173,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -3155,8 +3215,16 @@
       <c r="BH13" s="3" t="inlineStr"/>
       <c r="BI13" s="3" t="inlineStr"/>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3361,182 +3429,206 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-08-15T18:41:48+08:00</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods beef plant closures come as severe drought makes U.S. cattle shortages worse</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>工廠停工</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>'-0.961</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNVWFkTW91a0NZVkdFZHRmTFc1c2lsRFFjQ0Q5R0FYUmRDd1hvNElSMXVBbEozd004aFo2cDd0SkRZVkNETjV1WGpJRE5FVDd0dlZIYnBFcnFTQzk4MUNuZXBLQ3VNTnEyQmtnTXhoNnhrSVd3R2QzZjZFQUZVTFNhSjBuS3lmVzJFQ0Uzc3ZObm1FRVYyNE1pNlJBMUNkaW0yQkNCRy1xcUVOQ0EzOWhFZnlqOVd2U1FLYnhqc2FjLU9ldExtcVU2OXlkd3BtRDFHcWp0RlVUSXpSUDVfYmF5Zl80aGI5MVdHV09qMA?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>嚴重乾旱導緻美國牛短缺加劇，泰森食品牛肉工廠關閉</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>FACTORY_SHUTDOWN</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>drought</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>c89e6c169d124fd295faf0a72c62f894</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>3a15d0622668578770454017</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>37ddcbc165e51de0391d3854</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>'-0.961</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNVWFkTW91a0NZVkdFZHRmTFc1c2lsRFFjQ0Q5R0FYUmRDd1hvNElSMXVBbEozd004aFo2cDd0SkRZVkNETjV1WGpJRE5FVDd0dlZIYnBFcnFTQzk4MUNuZXBLQ3VNTnEyQmtnTXhoNnhrSVd3R2QzZjZFQUZVTFNhSjBuS3lmVzJFQ0Uzc3ZObm1FRVYyNE1pNlJBMUNkaW0yQkNCRy1xcUVOQ0EzOWhFZnlqOVd2U1FLYnhqc2FjLU9ldExtcVU2OXlkd3BtRDFHcWp0RlVUSXpSUDVfYmF5Zl80aGI5MVdHV09qMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>Bundle</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>嚴重乾旱導緻美國牛短缺加劇，泰森食品牛肉工廠關閉</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>drought</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>3a15d0622668578770454017</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>37ddcbc165e51de0391d3854</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr">
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="3" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="3" t="inlineStr">
+      <c r="BG15" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3572,28 +3664,32 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3637,7 +3733,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -3646,7 +3742,11 @@
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>a6df8e0e2fbc46b180cb28ccd19ecfd5</t>
+        </is>
+      </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
           <t>dbbe8d38fcdb2b45b95cc1f1</t>
@@ -3667,7 +3767,11 @@
       <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="inlineStr"/>
       <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="3" t="inlineStr"/>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
@@ -3711,10 +3815,22 @@
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
-      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr"/>
-      <c r="BL16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4150,28 +4266,32 @@
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4215,7 +4335,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -4224,7 +4344,11 @@
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>d6aa9276dac941d3a0ae7ae1aa5a2c0a</t>
+        </is>
+      </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
           <t>a5bb5cebe411f584848f2110</t>
@@ -4245,7 +4369,11 @@
       <c r="AL19" s="3" t="inlineStr"/>
       <c r="AM19" s="3" t="inlineStr"/>
       <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="3" t="inlineStr"/>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr"/>
@@ -4289,10 +4417,22 @@
         </is>
       </c>
       <c r="BH19" s="3" t="inlineStr"/>
-      <c r="BI19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="3" t="inlineStr"/>
-      <c r="BK19" s="3" t="inlineStr"/>
-      <c r="BL19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4720,28 +4860,32 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4785,7 +4929,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -4794,7 +4938,11 @@
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>fefcfe9114fd41138d4bf353767a0345</t>
+        </is>
+      </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>4a352a94862d236d2f1c6119</t>
@@ -4815,7 +4963,11 @@
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="3" t="inlineStr"/>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
@@ -4851,10 +5003,22 @@
         </is>
       </c>
       <c r="BH22" s="3" t="inlineStr"/>
-      <c r="BI22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="3" t="inlineStr"/>
-      <c r="BK22" s="3" t="inlineStr"/>
-      <c r="BL22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5868,28 +6032,32 @@
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -5933,7 +6101,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -5942,7 +6110,11 @@
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr"/>
-      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>c75483088ae647c686c7ffe5d00b510a</t>
+        </is>
+      </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
           <t>e87ccc0af73b5605b46ca669</t>
@@ -5963,7 +6135,11 @@
       <c r="AL28" s="3" t="inlineStr"/>
       <c r="AM28" s="3" t="inlineStr"/>
       <c r="AN28" s="3" t="inlineStr"/>
-      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="3" t="inlineStr"/>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr"/>
@@ -5999,10 +6175,22 @@
         </is>
       </c>
       <c r="BH28" s="3" t="inlineStr"/>
-      <c r="BI28" s="3" t="inlineStr"/>
+      <c r="BI28" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="3" t="inlineStr"/>
-      <c r="BK28" s="3" t="inlineStr"/>
-      <c r="BL28" s="3" t="inlineStr"/>
+      <c r="BK28" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -6038,28 +6226,32 @@
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6103,7 +6295,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -6112,7 +6304,11 @@
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr"/>
-      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>68671de4ea6b45b1b86dc9bd243eb1dd</t>
+        </is>
+      </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
           <t>75a6dd147499ed158b52f0a8</t>
@@ -6133,7 +6329,11 @@
       <c r="AL29" s="3" t="inlineStr"/>
       <c r="AM29" s="3" t="inlineStr"/>
       <c r="AN29" s="3" t="inlineStr"/>
-      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="3" t="inlineStr"/>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr"/>
@@ -6177,10 +6377,22 @@
         </is>
       </c>
       <c r="BH29" s="3" t="inlineStr"/>
-      <c r="BI29" s="3" t="inlineStr"/>
+      <c r="BI29" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ29" s="3" t="inlineStr"/>
-      <c r="BK29" s="3" t="inlineStr"/>
-      <c r="BL29" s="3" t="inlineStr"/>
+      <c r="BK29" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -6421,13 +6633,17 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -6480,7 +6696,11 @@
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr"/>
-      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>b3930af6d8e9400497511e61b82a3e67</t>
+        </is>
+      </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
           <t>21e84994835ba026a27a1bb6</t>
@@ -6501,7 +6721,11 @@
       <c r="AL31" s="3" t="inlineStr"/>
       <c r="AM31" s="3" t="inlineStr"/>
       <c r="AN31" s="3" t="inlineStr"/>
-      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="3" t="inlineStr"/>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr"/>
@@ -6539,8 +6763,16 @@
       <c r="BH31" s="3" t="inlineStr"/>
       <c r="BI31" s="3" t="inlineStr"/>
       <c r="BJ31" s="3" t="inlineStr"/>
-      <c r="BK31" s="3" t="inlineStr"/>
-      <c r="BL31" s="3" t="inlineStr"/>
+      <c r="BK31" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6576,28 +6808,32 @@
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -6641,7 +6877,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -6650,7 +6886,11 @@
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr"/>
-      <c r="AB32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>33fed7d8726248ad9ef5736da19b2bf8</t>
+        </is>
+      </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
           <t>3e88b7b73cc6616daa1a2e9d</t>
@@ -6671,7 +6911,11 @@
       <c r="AL32" s="3" t="inlineStr"/>
       <c r="AM32" s="3" t="inlineStr"/>
       <c r="AN32" s="3" t="inlineStr"/>
-      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="3" t="inlineStr"/>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr"/>
@@ -6707,10 +6951,22 @@
         </is>
       </c>
       <c r="BH32" s="3" t="inlineStr"/>
-      <c r="BI32" s="3" t="inlineStr"/>
+      <c r="BI32" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ32" s="3" t="inlineStr"/>
-      <c r="BK32" s="3" t="inlineStr"/>
-      <c r="BL32" s="3" t="inlineStr"/>
+      <c r="BK32" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -7728,28 +7984,32 @@
       <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -7793,7 +8053,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -7802,7 +8062,11 @@
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr"/>
-      <c r="AB38" s="3" t="inlineStr"/>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>e0bc5a25960a4390a7cd46382c3a51e4</t>
+        </is>
+      </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
           <t>fac2a736323a80e3b6a642e9</t>
@@ -7823,7 +8087,11 @@
       <c r="AL38" s="3" t="inlineStr"/>
       <c r="AM38" s="3" t="inlineStr"/>
       <c r="AN38" s="3" t="inlineStr"/>
-      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="3" t="inlineStr"/>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr"/>
@@ -7859,10 +8127,22 @@
         </is>
       </c>
       <c r="BH38" s="3" t="inlineStr"/>
-      <c r="BI38" s="3" t="inlineStr"/>
+      <c r="BI38" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ38" s="3" t="inlineStr"/>
-      <c r="BK38" s="3" t="inlineStr"/>
-      <c r="BL38" s="3" t="inlineStr"/>
+      <c r="BK38" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -8088,28 +8368,32 @@
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -8153,7 +8437,7 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -8162,7 +8446,11 @@
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr"/>
-      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>7bc19bf667e74e499afa07e43ef20d06</t>
+        </is>
+      </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
           <t>104206e75820a96d472fbbd8</t>
@@ -8183,7 +8471,11 @@
       <c r="AL40" s="3" t="inlineStr"/>
       <c r="AM40" s="3" t="inlineStr"/>
       <c r="AN40" s="3" t="inlineStr"/>
-      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP40" s="3" t="inlineStr"/>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr"/>
@@ -8227,10 +8519,22 @@
         </is>
       </c>
       <c r="BH40" s="3" t="inlineStr"/>
-      <c r="BI40" s="3" t="inlineStr"/>
+      <c r="BI40" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ40" s="3" t="inlineStr"/>
-      <c r="BK40" s="3" t="inlineStr"/>
-      <c r="BL40" s="3" t="inlineStr"/>
+      <c r="BK40" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -9069,13 +9373,17 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -9128,7 +9436,11 @@
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr"/>
-      <c r="AB45" s="3" t="inlineStr"/>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>8c67a39f8f4d44f8906633a27f24e4d9</t>
+        </is>
+      </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
           <t>3125d011aa02920bd599ea01</t>
@@ -9149,7 +9461,11 @@
       <c r="AL45" s="3" t="inlineStr"/>
       <c r="AM45" s="3" t="inlineStr"/>
       <c r="AN45" s="3" t="inlineStr"/>
-      <c r="AO45" s="3" t="inlineStr"/>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP45" s="3" t="inlineStr"/>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr"/>
@@ -9187,8 +9503,16 @@
       <c r="BH45" s="3" t="inlineStr"/>
       <c r="BI45" s="3" t="inlineStr"/>
       <c r="BJ45" s="3" t="inlineStr"/>
-      <c r="BK45" s="3" t="inlineStr"/>
-      <c r="BL45" s="3" t="inlineStr"/>
+      <c r="BK45" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -10396,28 +10720,32 @@
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -10461,7 +10789,7 @@
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z52" s="3" t="inlineStr">
@@ -10470,7 +10798,11 @@
         </is>
       </c>
       <c r="AA52" s="3" t="inlineStr"/>
-      <c r="AB52" s="3" t="inlineStr"/>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>2419a9caa71e481f83e47149ae25594e</t>
+        </is>
+      </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
           <t>a3254ede063c89af9225f282</t>
@@ -10491,7 +10823,11 @@
       <c r="AL52" s="3" t="inlineStr"/>
       <c r="AM52" s="3" t="inlineStr"/>
       <c r="AN52" s="3" t="inlineStr"/>
-      <c r="AO52" s="3" t="inlineStr"/>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP52" s="3" t="inlineStr"/>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr"/>
@@ -10535,10 +10871,22 @@
         </is>
       </c>
       <c r="BH52" s="3" t="inlineStr"/>
-      <c r="BI52" s="3" t="inlineStr"/>
+      <c r="BI52" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ52" s="3" t="inlineStr"/>
-      <c r="BK52" s="3" t="inlineStr"/>
-      <c r="BL52" s="3" t="inlineStr"/>
+      <c r="BK52" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -11317,182 +11665,206 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>2026-08-15T01:43:58+08:00</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods beef plant closures come as severe drought makes U.S. cattle shortages worse</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="3" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>工廠停工</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>'-0.961</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNSG1OMlVnREdUa2ljMGpjQV9SS01xWGI2ZE41WUZpNnU5SnBLMGpzOF90cGhxQTRZTGFaUDhWY2djNVQ5RW9lWTFjdDhGa1dJQVNfdmtNWnBUOUp5YmJaNWpVRXR5Mkw5eWRKNVN6Q1hfODZnd1pKdm42ZHdsZ09Kek92VFBXWEhNR0lhMkFwU3N5a3dWZy1jUEV1UmV6STdVOGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Fast Company</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>嚴重乾旱導緻美國牛短缺加劇，泰森食品牛肉工廠關閉</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>FACTORY_SHUTDOWN</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>drought</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>c2d0ad76fd1848128ca6738d97473d86</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>d6addd8557ffea972afec449</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>9dc3fc8a1dd81c971025377c</t>
+        </is>
+      </c>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+      <c r="AK57" s="2" t="inlineStr"/>
+      <c r="AL57" s="2" t="inlineStr"/>
+      <c r="AM57" s="2" t="inlineStr"/>
+      <c r="AN57" s="2" t="inlineStr"/>
+      <c r="AO57" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>'-0.961</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="inlineStr"/>
-      <c r="Q57" s="3" t="inlineStr"/>
-      <c r="R57" s="3" t="inlineStr"/>
-      <c r="S57" s="3" t="inlineStr"/>
-      <c r="T57" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U57" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNSG1OMlVnREdUa2ljMGpjQV9SS01xWGI2ZE41WUZpNnU5SnBLMGpzOF90cGhxQTRZTGFaUDhWY2djNVQ5RW9lWTFjdDhGa1dJQVNfdmtNWnBUOUp5YmJaNWpVRXR5Mkw5eWRKNVN6Q1hfODZnd1pKdm42ZHdsZ09Kek92VFBXWEhNR0lhMkFwU3N5a3dWZy1jUEV1UmV6STdVOGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V57" s="3" t="inlineStr">
-        <is>
-          <t>Fast Company</t>
-        </is>
-      </c>
-      <c r="W57" s="3" t="inlineStr">
-        <is>
-          <t>嚴重乾旱導緻美國牛短缺加劇，泰森食品牛肉工廠關閉</t>
-        </is>
-      </c>
-      <c r="X57" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z57" s="3" t="inlineStr">
-        <is>
-          <t>drought</t>
-        </is>
-      </c>
-      <c r="AA57" s="3" t="inlineStr"/>
-      <c r="AB57" s="3" t="inlineStr"/>
-      <c r="AC57" s="3" t="inlineStr">
-        <is>
-          <t>d6addd8557ffea972afec449</t>
-        </is>
-      </c>
-      <c r="AD57" s="3" t="inlineStr">
-        <is>
-          <t>9dc3fc8a1dd81c971025377c</t>
-        </is>
-      </c>
-      <c r="AE57" s="3" t="inlineStr"/>
-      <c r="AF57" s="3" t="inlineStr"/>
-      <c r="AG57" s="3" t="inlineStr"/>
-      <c r="AH57" s="3" t="inlineStr"/>
-      <c r="AI57" s="3" t="inlineStr"/>
-      <c r="AJ57" s="3" t="inlineStr"/>
-      <c r="AK57" s="3" t="inlineStr"/>
-      <c r="AL57" s="3" t="inlineStr"/>
-      <c r="AM57" s="3" t="inlineStr"/>
-      <c r="AN57" s="3" t="inlineStr"/>
-      <c r="AO57" s="3" t="inlineStr"/>
-      <c r="AP57" s="3" t="inlineStr"/>
-      <c r="AQ57" s="3" t="inlineStr"/>
-      <c r="AR57" s="3" t="inlineStr"/>
-      <c r="AS57" s="3" t="inlineStr"/>
-      <c r="AT57" s="3" t="inlineStr"/>
-      <c r="AU57" s="3" t="inlineStr"/>
-      <c r="AV57" s="3" t="inlineStr"/>
-      <c r="AW57" s="3" t="inlineStr">
+      <c r="AP57" s="2" t="inlineStr"/>
+      <c r="AQ57" s="2" t="inlineStr"/>
+      <c r="AR57" s="2" t="inlineStr"/>
+      <c r="AS57" s="2" t="inlineStr"/>
+      <c r="AT57" s="2" t="inlineStr"/>
+      <c r="AU57" s="2" t="inlineStr"/>
+      <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX57" s="3" t="inlineStr"/>
-      <c r="AY57" s="3" t="inlineStr"/>
-      <c r="AZ57" s="3" t="inlineStr"/>
-      <c r="BA57" s="3" t="inlineStr"/>
-      <c r="BB57" s="3" t="inlineStr">
+      <c r="AX57" s="2" t="inlineStr"/>
+      <c r="AY57" s="2" t="inlineStr"/>
+      <c r="AZ57" s="2" t="inlineStr"/>
+      <c r="BA57" s="2" t="inlineStr"/>
+      <c r="BB57" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="BC57" s="3" t="inlineStr">
+      <c r="BC57" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD57" s="3" t="inlineStr"/>
-      <c r="BE57" s="3" t="inlineStr">
+      <c r="BD57" s="2" t="inlineStr"/>
+      <c r="BE57" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF57" s="3" t="inlineStr">
+      <c r="BF57" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG57" s="3" t="inlineStr">
+      <c r="BG57" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH57" s="3" t="inlineStr"/>
-      <c r="BI57" s="3" t="inlineStr"/>
-      <c r="BJ57" s="3" t="inlineStr"/>
-      <c r="BK57" s="3" t="inlineStr"/>
-      <c r="BL57" s="3" t="inlineStr"/>
+      <c r="BH57" s="2" t="inlineStr"/>
+      <c r="BI57" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ57" s="2" t="inlineStr"/>
+      <c r="BK57" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -11722,28 +12094,32 @@
       <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -11787,7 +12163,7 @@
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z59" s="3" t="inlineStr">
@@ -11796,7 +12172,11 @@
         </is>
       </c>
       <c r="AA59" s="3" t="inlineStr"/>
-      <c r="AB59" s="3" t="inlineStr"/>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>501af12b3c464752baa0d520c4145544</t>
+        </is>
+      </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
           <t>817cea2c0b0086097ffb25d5</t>
@@ -11817,7 +12197,11 @@
       <c r="AL59" s="3" t="inlineStr"/>
       <c r="AM59" s="3" t="inlineStr"/>
       <c r="AN59" s="3" t="inlineStr"/>
-      <c r="AO59" s="3" t="inlineStr"/>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP59" s="3" t="inlineStr"/>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr"/>
@@ -11861,10 +12245,22 @@
         </is>
       </c>
       <c r="BH59" s="3" t="inlineStr"/>
-      <c r="BI59" s="3" t="inlineStr"/>
+      <c r="BI59" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ59" s="3" t="inlineStr"/>
-      <c r="BK59" s="3" t="inlineStr"/>
-      <c r="BL59" s="3" t="inlineStr"/>
+      <c r="BK59" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL59" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -12094,28 +12490,32 @@
       <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -12159,7 +12559,7 @@
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z61" s="3" t="inlineStr">
@@ -12168,7 +12568,11 @@
         </is>
       </c>
       <c r="AA61" s="3" t="inlineStr"/>
-      <c r="AB61" s="3" t="inlineStr"/>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>d619057261ef472f8f2931e291ea0e89</t>
+        </is>
+      </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
           <t>f5cf98e3155e7fde75783a83</t>
@@ -12189,7 +12593,11 @@
       <c r="AL61" s="3" t="inlineStr"/>
       <c r="AM61" s="3" t="inlineStr"/>
       <c r="AN61" s="3" t="inlineStr"/>
-      <c r="AO61" s="3" t="inlineStr"/>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP61" s="3" t="inlineStr"/>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr"/>
@@ -12225,10 +12633,22 @@
         </is>
       </c>
       <c r="BH61" s="3" t="inlineStr"/>
-      <c r="BI61" s="3" t="inlineStr"/>
+      <c r="BI61" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ61" s="3" t="inlineStr"/>
-      <c r="BK61" s="3" t="inlineStr"/>
-      <c r="BL61" s="3" t="inlineStr"/>
+      <c r="BK61" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL61" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -12828,7 +13248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL21"/>
+  <dimension ref="A1:BL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14008,600 +14428,596 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nike, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-15T19:21:22+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>NKE Stock Ticks Higher After Hours on Second Round of Layoffs In 2026</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T21:08:23+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Coinbase (COIN) Stock Still Looks Overvalued Despite New York Probe</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.515</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.823</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNTHNjTU9raHhwdUtpamJRODJFSk9pbHVCdDJoVUg1QzFBalAtaGxyZkFMT2VxcE1OSXhjVUhLUnVpb3RpVHJzajI4ZUc4d0FUR0NnaFNwVUxGbHMxMHl6OFZqSzVqSEM0eHF1UWxWUnEtcTZNUUtQUzlOekxuRlU2ZEp4b2kwU3lIUjFvRjZtdENsWWVuaHUwWjNCU3BRUERLZjkxY3h2TXdWSGdrd1hCcnU1OFFrTkRVRWEtWVJWejdkVFd5OUdPQm1B?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Stocktwits</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>NKE 股價盤後走高，因 2026 年第二輪裁員</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>6bace1673fa14131ac8a564fd9fe0a0c</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>c53b9ce318d9c0881e2f25b9</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>899d4b4bc63727bb759257f8</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxONzc5SFdHcTJZSm1BWmw3Tm1oeGlHaXdDclJYbnY0TFZVWmlfNjdYUjRmUFVOZ1ZZaXB0eHFrQWl2M01JNHR4YTI3LWJXYVl5WU1sTU9OYWNiaW40c1VYV3ZYdlZrRXFhUjhhMEpDQVN6S0xJa3FzbXhxRVlYenNzTW9vekxZLS1sRFVGazdIMk5Dd0VVZmhlUzVpOHk?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>儘管紐約調查，Coinbase (COIN) 股票看起來仍然被高估</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>overvalued</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>186e905bd4d743c7bd79ec88b35d11f8</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>3b2b8a529ce20d3abdfd51d2</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>6c89cb0cd0f4131e12a66479</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr"/>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr"/>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:54:08.043808+08:00</t>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15T19:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Equifax Agrees to $100M Settlement over Error That Changed Millions of Credit Scores</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Nike, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T19:21:22+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>NKE Stock Ticks Higher After Hours on Second Round of Layoffs In 2026</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>0.138</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>'-0.515</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE04N1QwTHJEMDN6MEMyN2stLXNiaTRnM1U0UXRLcjZiQ2NoQ2NCSUd0aU1GTUZGdWVBQzZCS1N3WWVZYjBacE14VklXejJuelF0ZHFxUDlGRFRiX3JTMmxSdFVmN2lNWXg3bzFCVy12ek9pU3VaSy1BS2ZIdEk?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>en.econostrum.info</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
-        <is>
-          <t>Equifax 同意就改變數百萬信用評分的錯誤支付 1 億美元和解</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>968e8941a83f41e9ad864d04834d248f</t>
-        </is>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>82af173a59ab396756f945d8</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>ae062e0ae775d59af71e95dc</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNTHNjTU9raHhwdUtpamJRODJFSk9pbHVCdDJoVUg1QzFBalAtaGxyZkFMT2VxcE1OSXhjVUhLUnVpb3RpVHJzajI4ZUc4d0FUR0NnaFNwVUxGbHMxMHl6OFZqSzVqSEM0eHF1UWxWUnEtcTZNUUtQUzlOekxuRlU2ZEp4b2kwU3lIUjFvRjZtdENsWWVuaHUwWjNCU3BRUERLZjkxY3h2TXdWSGdrd1hCcnU1OFFrTkRVRWEtWVJWejdkVFd5OUdPQm1B?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>NKE 股價盤後走高，因 2026 年第二輪裁員</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>6bace1673fa14131ac8a564fd9fe0a0c</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>c53b9ce318d9c0881e2f25b9</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>899d4b4bc63727bb759257f8</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="4" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
-      <c r="BI7" s="4" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr">
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>LVS</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Las Vegas Sands Corp.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-15T18:27:45+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>How Investors Are Reacting To Las Vegas Sands (LVS) Earnings Miss And Bearish Analyst Revisions</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Equifax, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T19:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Equifax Agrees to $100M Settlement over Error That Changed Millions of Credit Scores</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>'-0.611</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>0.138</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPcFd5WVJ3aG1vdUVWMnRtbHFuaVhZZ3FHSG11LXc4aExqc2ViVmlIRkIwZTl0Q2hwWDZ6d3htdDg0SUhTamthbUk1M1UyV2EtTnVmdURDSlIyZ01pNkVJY0dyYU12UlY0bTRPWTR5VnZJS2NFVENUUUJvY1c0QndzQnlCUFZnNV9fX0JUWmNNcU1xVU1GbDBwcWxPcDVuTzd2MVI4WDdHZE45ZFpaa3ZndjY3SHNlWjZQZkxJWW9ES3ZLUU5mbjk1cGdaQkd5NzRBS05hQm9tb9IB3AFBVV95cUxORkpYekRlY0FCZjRoTXp1LW84bE11UWRIandDRzlSNUZUcEcwalhlVU5oVzgxYWNLaldvd0FIZmRyVHJ3cEhzOVNiY3NSREpOTU9tQkdoWFRaZlJhbm5JeFZ5YUtFV3NCM2pjQktVNlNMYTdHRElVQ09xSkxPTVFzX1Y4aTBXeWZCNWJJMm1WVnZ2bkd3SGFjTnFKVEhqcGhUVVBGdVJQek9xZkVxakktMHY1RU13ZTVMWHhEYjVBV3ZaakZRY2UwaVp3eWktaWgzcUVWZUgxeXRXYXEx?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>投資者對拉斯維加斯金沙集團 (LVS) 盈利低於預期和分析師悲觀的修正有何反應</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1d68dcfaf0964802b6dbb3807f526f5c</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>f17d91444141fe404483338d</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>72f1c0826466cb8774c826f9</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE04N1QwTHJEMDN6MEMyN2stLXNiaTRnM1U0UXRLcjZiQ2NoQ2NCSUd0aU1GTUZGdWVBQzZCS1N3WWVZYjBacE14VklXejJuelF0ZHFxUDlGRFRiX3JTMmxSdFVmN2lNWXg3bzFCVy12ek9pU3VaSy1BS2ZIdEk?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>en.econostrum.info</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>Equifax 同意就改變數百萬信用評分的錯誤支付 1 億美元和解</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>968e8941a83f41e9ad864d04834d248f</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>82af173a59ab396756f945d8</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>ae062e0ae775d59af71e95dc</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="inlineStr"/>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr"/>
-      <c r="AW8" s="2" t="inlineStr">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr"/>
-      <c r="AZ8" s="2" t="inlineStr"/>
-      <c r="BA8" s="2" t="inlineStr"/>
-      <c r="BB8" s="2" t="inlineStr">
-        <is>
-          <t>LVS</t>
-        </is>
-      </c>
-      <c r="BC8" s="2" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="2" t="inlineStr"/>
-      <c r="BE8" s="2" t="inlineStr">
-        <is>
-          <t>https://investor.sands.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG8" s="2" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
-      <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG8" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:54:08.043808+08:00</t>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
@@ -14618,22 +15034,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T17:16:54+08:00</t>
+          <t>2026-08-15T18:41:48+08:00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Crypto Stocks Under Pressure – HOOD Slumps After Earnings Miss, While COIN And CRCL Drift Lower</t>
+          <t>Tyson Foods beef plant closures come as severe drought makes U.S. cattle shortages worse</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -14644,7 +15060,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>工廠停工</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14674,7 +15090,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>'-0.939</t>
+          <t>'-0.961</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -14688,48 +15104,48 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPZ0VWSEhDLXpvam9LRGh6QVNQa0pHdVFYSkdlTnM4SGRraDFSaml2ZFEzZDk0ZzBPTWh5bVNqZ2x1aUd2NUl3UjdqYkl5WU5abS1maHY0SXNUOUlaSlZadk1hUFRXQVZBSzdjallSX0dBbmZXcHJMcEp4WUVRR0Q2VDFwRXRMUV9PenlRaXdvRnFnek8xZXpWT05uYzY4dmhqZno5aEx6WXRQS2R2U3ZLSnFwN2g1ZDN5UGNhdjF4NG1JZ0ZFNnJHcE15MlotUndrWlBsY3dfVFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNVWFkTW91a0NZVkdFZHRmTFc1c2lsRFFjQ0Q5R0FYUmRDd1hvNElSMXVBbEozd004aFo2cDd0SkRZVkNETjV1WGpJRE5FVDd0dlZIYnBFcnFTQzk4MUNuZXBLQ3VNTnEyQmtnTXhoNnhrSVd3R2QzZjZFQUZVTFNhSjBuS3lmVzJFQ0Uzc3ZObm1FRVYyNE1pNlJBMUNkaW0yQkNCRy1xcUVOQ0EzOWhFZnlqOVd2U1FLYnhqc2FjLU9ldExtcVU2OXlkd3BtRDFHcWp0RlVUSXpSUDVfYmF5Zl80aGI5MVdHV09qMA?oc=5</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>Bundle</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>加密貨幣股票面臨壓力——HOOD 在盈利不佳後暴跌，而 COIN 和 CRCL 則走低</t>
+          <t>嚴重乾旱導緻美國牛短缺加劇，泰森食品牛肉工廠關閉</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>FACTORY_SHUTDOWN</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>earnings miss</t>
+          <t>drought</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>d6b7c60008274ad092ae04039887f91c</t>
+          <t>c89e6c169d124fd295faf0a72c62f894</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>415e122ee560b6a926d060a7</t>
+          <t>3a15d0622668578770454017</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>e4ec98457401625562f7434d</t>
+          <t>37ddcbc165e51de0391d3854</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr"/>
@@ -14756,7 +15172,7 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" s="2" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX9" s="2" t="inlineStr"/>
@@ -14765,7 +15181,7 @@
       <c r="BA9" s="2" t="inlineStr"/>
       <c r="BB9" s="2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="BC9" s="2" t="inlineStr">
@@ -14776,12 +15192,12 @@
       <c r="BD9" s="2" t="inlineStr"/>
       <c r="BE9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
       <c r="BG9" s="2" t="inlineStr">
@@ -14790,7 +15206,11 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
       <c r="BK9" s="2" t="inlineStr">
         <is>
@@ -14799,7 +15219,7 @@
       </c>
       <c r="BL9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T15:54:08.043808+08:00</t>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
         </is>
       </c>
     </row>
@@ -14816,22 +15236,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Las Vegas Sands Corp.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T16:56:10+08:00</t>
+          <t>2026-08-15T18:27:45+08:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>AAPL Stock Heads For Worst Single-Day Fall In Over A Year — Wall Street Warns Apple’s AI Supply Chain Headwinds Are Far From Over</t>
+          <t>How Investors Are Reacting To Las Vegas Sands (LVS) Earnings Miss And Bearish Analyst Revisions</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -14842,7 +15262,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>財報不如預期</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14872,7 +15292,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>'-0.945</t>
+          <t>'-0.611</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -14886,48 +15306,48 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQM0NVeHRMVUhYQzcxTHE1RWR4c1BlOXZLa3VxYjZSNmhYci1ZamtvNGRDalktNlhmM1kwOE5IMmZUR05hWXMtb2lEUnN3S1BZNFE4c2s5emM4NGVnMlRXaFpQWm52S3haY191RW1KSEVwUGNJVTJEVmk1cnZhQmV1eE9VM1MwLXQ2c2pqeC1wZ1YyYnFMUmg2MFZ3Ri1aU21jN3F2aTI1S0ZhYTIzOGJXVDdxNzdBZ2FBc2JTOG9zMFZUMWJRbjdlWTYyWVRDMDlnUDVsN3hIOXNyM3lKaEQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPcFd5WVJ3aG1vdUVWMnRtbHFuaVhZZ3FHSG11LXc4aExqc2ViVmlIRkIwZTl0Q2hwWDZ6d3htdDg0SUhTamthbUk1M1UyV2EtTnVmdURDSlIyZ01pNkVJY0dyYU12UlY0bTRPWTR5VnZJS2NFVENUUUJvY1c0QndzQnlCUFZnNV9fX0JUWmNNcU1xVU1GbDBwcWxPcDVuTzd2MVI4WDdHZE45ZFpaa3ZndjY3SHNlWjZQZkxJWW9ES3ZLUU5mbjk1cGdaQkd5NzRBS05hQm9tb9IB3AFBVV95cUxORkpYekRlY0FCZjRoTXp1LW84bE11UWRIandDRzlSNUZUcEcwalhlVU5oVzgxYWNLaldvd0FIZmRyVHJ3cEhzOVNiY3NSREpOTU9tQkdoWFRaZlJhbm5JeFZ5YUtFV3NCM2pjQktVNlNMYTdHRElVQ09xSkxPTVFzX1Y4aTBXeWZCNWJJMm1WVnZ2bkd3SGFjTnFKVEhqcGhUVVBGdVJQek9xZkVxakktMHY1RU13ZTVMWHhEYjVBV3ZaakZRY2UwaVp3eWktaWgzcUVWZUgxeXRXYXEx?oc=5</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>蘋果股價將迎來一年多來最嚴重的單日跌幅——華爾街警告蘋果的人工智慧供應鏈逆風還遠未結束</t>
+          <t>投資者對拉斯維加斯金沙集團 (LVS) 盈利低於預期和分析師悲觀的修正有何反應</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>EARNINGS_MISS</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>supply chain</t>
+          <t>earnings miss</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>07706ecb903e4320881f1526bfd71ad2</t>
+          <t>1d68dcfaf0964802b6dbb3807f526f5c</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9c8cb5d2ce9ae557fff5ec97</t>
+          <t>f17d91444141fe404483338d</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>c28b9130df3e27acf925d78d</t>
+          <t>72f1c0826466cb8774c826f9</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
@@ -14954,7 +15374,7 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" s="2" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX10" s="2" t="inlineStr"/>
@@ -14963,7 +15383,7 @@
       <c r="BA10" s="2" t="inlineStr"/>
       <c r="BB10" s="2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
@@ -14974,17 +15394,17 @@
       <c r="BD10" s="2" t="inlineStr"/>
       <c r="BE10" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://investor.sands.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG10" s="2" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
@@ -15014,22 +15434,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Trade Desk (The)</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T16:46:02+08:00</t>
+          <t>2026-08-15T17:16:54+08:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>TTD Stock Sinks Over 26% On Earnings Miss, Weak Outlook — Retail Says Trade Desk’s Guidance Is The Real Problem</t>
+          <t>Crypto Stocks Under Pressure – HOOD Slumps After Earnings Miss, While COIN And CRCL Drift Lower</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -15070,7 +15490,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>'-0.957</t>
+          <t>'-0.939</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -15084,7 +15504,7 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOdmRQRTZXb1dhN3FTVGZ3allPME9nQ29TNnAwNnVoR1BmSDMtSjRqNlNUS3JwaVl2cEVkZTV1T2swb3lGSTBKTVY5aUY3NWF1T0QtVFJVa2xNNWRPaE1xdWdRWDlseTdhMFQ4cmE5ZzBuZ24tR0ZZUE9iUnV5T1RuZDJza3JzVW9OYnJHMkZxLUNCV0QwZGotZ2dDSkZVVnNUWmsxMWhXelpqRF9Md3hGWGdCQThhV1pOSmQ5cUFrZU8zb0dKaElPbkNHajV1TVpYMjNiTmdYN1c2eGVVdUJ6dEc5TmQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPZ0VWSEhDLXpvam9LRGh6QVNQa0pHdVFYSkdlTnM4SGRraDFSaml2ZFEzZDk0ZzBPTWh5bVNqZ2x1aUd2NUl3UjdqYkl5WU5abS1maHY0SXNUOUlaSlZadk1hUFRXQVZBSzdjallSX0dBbmZXcHJMcEp4WUVRR0Q2VDFwRXRMUV9PenlRaXdvRnFnek8xZXpWT05uYzY4dmhqZno5aEx6WXRQS2R2U3ZLSnFwN2g1ZDN5UGNhdjF4NG1JZ0ZFNnJHcE15MlotUndrWlBsY3dfVFk?oc=5</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -15094,7 +15514,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>TTD 股價因盈利不佳和前景疲軟而下跌超過 26% — 零售業表示 Trade Desk 的指導才是真正的問題</t>
+          <t>加密貨幣股票面臨壓力——HOOD 在盈利不佳後暴跌，而 COIN 和 CRCL 則走低</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -15115,17 +15535,17 @@
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>2e7e2628b5a842edba387b6dcef23fdf</t>
+          <t>d6b7c60008274ad092ae04039887f91c</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>e0cfdf9d4f7c60a5918167c0</t>
+          <t>415e122ee560b6a926d060a7</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9d95623c9dd011b866d26579</t>
+          <t>e4ec98457401625562f7434d</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr"/>
@@ -15150,14 +15570,18 @@
       <c r="AT11" s="2" t="inlineStr"/>
       <c r="AU11" s="2" t="inlineStr"/>
       <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX11" s="2" t="inlineStr"/>
       <c r="AY11" s="2" t="inlineStr"/>
       <c r="AZ11" s="2" t="inlineStr"/>
       <c r="BA11" s="2" t="inlineStr"/>
       <c r="BB11" s="2" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="BC11" s="2" t="inlineStr">
@@ -15168,13 +15592,17 @@
       <c r="BD11" s="2" t="inlineStr"/>
       <c r="BE11" s="2" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="2" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG11" s="2" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
@@ -15192,580 +15620,588 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15T08:48:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Corteva To Pay $3.1M In Ark. AG's Pesticides Antitrust Suit</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T16:56:10+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>AAPL Stock Heads For Worst Single-Day Fall In Over A Year — Wall Street Warns Apple’s AI Supply Chain Headwinds Are Far From Over</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>供應鏈中斷</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>'-0.074</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>'-0.945</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFA0TFJYNTVkYmhLTV9RTFpBTElyZEJwT1FHT3M0MXBGS1Y0YlF2MXZkeVZUQ2NOT2ZPbkJselJraXdtMUhqVk9lbnNwSG5PZFF6MEQ4dFR30gFWQVVfeXFMUDRMUlg1NWRiaEtNX1FMWkFMSXJkQnBPUUdPczQxcEZLVjRiUXYxdmR5VlRDY05PZk9uQmx6Umtpd20xSGpWT2Vuc3BIbk9kUXowRDh0VHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Law360</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>Corteva 將在 Ark. AG 農藥反壟斷訴訟中支付 310 萬美元</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t>532411c56a0a482885ad9726595d07f5</t>
-        </is>
-      </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>a070d99a0f8937cb71862e0d</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>46ecea8dff1c19fe72abb3e9</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQM0NVeHRMVUhYQzcxTHE1RWR4c1BlOXZLa3VxYjZSNmhYci1ZamtvNGRDalktNlhmM1kwOE5IMmZUR05hWXMtb2lEUnN3S1BZNFE4c2s5emM4NGVnMlRXaFpQWm52S3haY191RW1KSEVwUGNJVTJEVmk1cnZhQmV1eE9VM1MwLXQ2c2pqeC1wZ1YyYnFMUmg2MFZ3Ri1aU21jN3F2aTI1S0ZhYTIzOGJXVDdxNzdBZ2FBc2JTOG9zMFZUMWJRbjdlWTYyWVRDMDlnUDVsN3hIOXNyM3lKaEQ4?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>蘋果股價將迎來一年多來最嚴重的單日跌幅——華爾街警告蘋果的人工智慧供應鏈逆風還遠未結束</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>07706ecb903e4320881f1526bfd71ad2</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>9c8cb5d2ce9ae557fff5ec97</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>c28b9130df3e27acf925d78d</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr">
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15T08:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>PNR Alert: Hagens Berman Notifies Pentair plc (NYSE: PNR) Investors of Expanded Class Period in New Securities Class Action Lawsuit and Upcoming Lead Plaintiff Deadline</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Trade Desk (The)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T16:46:02+08:00</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TTD Stock Sinks Over 26% On Earnings Miss, Weak Outlook — Retail Says Trade Desk’s Guidance Is The Real Problem</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>財報不如預期</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>'-0.889</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>'-0.957</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgJBVV95cUxPblB0aHY3Qi0xS2hJSXVGd0FmTkxQenZhZFRsNTczSk93cHN3eng0TnYyNHpMTHdZc2FnaFFBT294OHllNjd0Q2Y3bDYtT3BEaW5Gc2x1YThiY2VKcm9aSjFxRm9xSWJSRmlwY0h1dW44TzFEc0NmMng0b29rNzhpWUxzNVJKd3VURDNxQ01DWnlicVBQczdsNC12VmstbVhCV0ZFd2tON0dCLVFNYVZYbHItM1NUd2NUQ1lrall5X19sSlhnQVVxQnl3V0l6QlRBMFl1RFVWdkJvRGZPTzVBb1JRMjFtZ1lpaUFkV0dfVzJkMF8tNmp5WHVwTUxNNTF6YnpYR1JqcEtIUXZkVHA1QWIwbzdaSTdOemxocUZLWWp4NVUzVTd1b21WNFd3OU9fVVMwOURSbUdkQ1ZnOHhCMnRn?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>PR Newswire</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t>PNR 警報：Hagens Berman 通知 Pentair plc（NYSE：PNR）投資者新證券集體訴訟的集體訴訟期限已延長，且首席原告截止日期即將到來</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>068e307f01664814a021033d7d9f7919</t>
-        </is>
-      </c>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>369955a25f251f3fa2c0f456</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>e383e1ec6967003c4dd50486</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOdmRQRTZXb1dhN3FTVGZ3allPME9nQ29TNnAwNnVoR1BmSDMtSjRqNlNUS3JwaVl2cEVkZTV1T2swb3lGSTBKTVY5aUY3NWF1T0QtVFJVa2xNNWRPaE1xdWdRWDlseTdhMFQ4cmE5ZzBuZ24tR0ZZUE9iUnV5T1RuZDJza3JzVW9OYnJHMkZxLUNCV0QwZGotZ2dDSkZVVnNUWmsxMWhXelpqRF9Md3hGWGdCQThhV1pOSmQ5cUFrZU8zb0dKaElPbkNHajV1TVpYMjNiTmdYN1c2eGVVdUJ6dEc5TmQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>TTD 股價因盈利不佳和前景疲軟而下跌超過 26% — 零售業表示 Trade Desk 的指導才是真正的問題</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>2e7e2628b5a842edba387b6dcef23fdf</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>e0cfdf9d4f7c60a5918167c0</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>9d95623c9dd011b866d26579</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC13" s="4" t="inlineStr">
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr"/>
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="BC13" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr">
+      <c r="BF13" s="2" t="inlineStr"/>
+      <c r="BG13" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="4" t="inlineStr"/>
-      <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr"/>
-      <c r="BK13" s="4" t="inlineStr">
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>General Motors</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-15T05:48:00+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>General Motors files notice for 361 layoffs at Lansing assembly sites</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T08:48:00+08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Corteva To Pay $3.1M In Ark. AG's Pesticides Antitrust Suit</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>'-0.961</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>'-0.074</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPc0x2QXl4OWNRQlE4M1hnc3ZSbTRCX1dyVVFYeERqdVctbHdueXZHMm4wZ2thamwyMVlQQi1KT3BZUXRoXzFpcWc1aV9BOVRZLTJRWXA3LXY0TjhwUnpDbTB2QXhhQWtWdExVUFJoZnQwU1ZYVTJ3Si00WDNXOG83d1RMVEE3aXVQcy1RcXRXUzNUeFRhU09CUVFHRmc3UU9icENaYXFTNDhpUEFwcVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>MLive.com</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>通用汽車發布蘭辛組裝廠裁員 361 人的通知</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>e04f7e98362c42a0ad23362115af0b3a</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>e2e6ef96b974fa9d958f7f1a</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>75f4b793594615b4b14a5867</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr"/>
-      <c r="AF14" s="2" t="inlineStr"/>
-      <c r="AG14" s="2" t="inlineStr"/>
-      <c r="AH14" s="2" t="inlineStr"/>
-      <c r="AI14" s="2" t="inlineStr"/>
-      <c r="AJ14" s="2" t="inlineStr"/>
-      <c r="AK14" s="2" t="inlineStr"/>
-      <c r="AL14" s="2" t="inlineStr"/>
-      <c r="AM14" s="2" t="inlineStr"/>
-      <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr">
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFA0TFJYNTVkYmhLTV9RTFpBTElyZEJwT1FHT3M0MXBGS1Y0YlF2MXZkeVZUQ2NOT2ZPbkJselJraXdtMUhqVk9lbnNwSG5PZFF6MEQ4dFR30gFWQVVfeXFMUDRMUlg1NWRiaEtNX1FMWkFMSXJkQnBPUUdPczQxcEZLVjRiUXYxdmR5VlRDY05PZk9uQmx6Umtpd20xSGpWT2Vuc3BIbk9kUXowRDh0VHc?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Law360</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>Corteva 將在 Ark. AG 農藥反壟斷訴訟中支付 310 萬美元</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>532411c56a0a482885ad9726595d07f5</t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>a070d99a0f8937cb71862e0d</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>46ecea8dff1c19fe72abb3e9</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr"/>
+      <c r="AF14" s="4" t="inlineStr"/>
+      <c r="AG14" s="4" t="inlineStr"/>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
+      <c r="AL14" s="4" t="inlineStr"/>
+      <c r="AM14" s="4" t="inlineStr"/>
+      <c r="AN14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP14" s="2" t="inlineStr"/>
-      <c r="AQ14" s="2" t="inlineStr"/>
-      <c r="AR14" s="2" t="inlineStr"/>
-      <c r="AS14" s="2" t="inlineStr"/>
-      <c r="AT14" s="2" t="inlineStr"/>
-      <c r="AU14" s="2" t="inlineStr"/>
-      <c r="AV14" s="2" t="inlineStr"/>
-      <c r="AW14" s="2" t="inlineStr"/>
-      <c r="AX14" s="2" t="inlineStr"/>
-      <c r="AY14" s="2" t="inlineStr"/>
-      <c r="AZ14" s="2" t="inlineStr"/>
-      <c r="BA14" s="2" t="inlineStr"/>
-      <c r="BB14" s="2" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BC14" s="2" t="inlineStr">
+      <c r="AP14" s="4" t="inlineStr"/>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="inlineStr"/>
+      <c r="AS14" s="4" t="inlineStr"/>
+      <c r="AT14" s="4" t="inlineStr"/>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX14" s="4" t="inlineStr"/>
+      <c r="AY14" s="4" t="inlineStr"/>
+      <c r="AZ14" s="4" t="inlineStr"/>
+      <c r="BA14" s="4" t="inlineStr"/>
+      <c r="BB14" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC14" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="2" t="inlineStr"/>
-      <c r="BE14" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF14" s="2" t="inlineStr"/>
-      <c r="BG14" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
-      <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr">
+      <c r="BD14" s="4" t="inlineStr"/>
+      <c r="BE14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG14" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:54:08.043808+08:00</t>
+      <c r="BL14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
@@ -15782,22 +16218,22 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T05:15:00+08:00</t>
+          <t>2026-08-15T08:30:00+08:00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Paramount-WBD Merger: David Ellison Complains About Cost Of States' Antitrust Suit</t>
+          <t>PNR Alert: Hagens Berman Notifies Pentair plc (NYSE: PNR) Investors of Expanded Class Period in New Securities Class Action Lawsuit and Upcoming Lead Plaintiff Deadline</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -15808,7 +16244,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>反壟斷調查</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -15838,7 +16274,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>'-0.929</t>
+          <t>'-0.889</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr"/>
@@ -15852,17 +16288,17 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxON3Vua0xBT0RuclpJSjR1b2pvd2xqX003REkzdFB2TXU2WnlPRDNEQlQxN1RhWjJMelhiZ0J0SkVaM2ZYMWZWd1dqTDdudndkeTJ2YkUyT3pGcEZjOERwUDB4QklHUXpEbk5HSEZQUXJjMEhtLUY5amxQWk5vWjhWaW5MWHh0UFR1QktiY0dGSzZxWGllWDc0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgJBVV95cUxPblB0aHY3Qi0xS2hJSXVGd0FmTkxQenZhZFRsNTczSk93cHN3eng0TnYyNHpMTHdZc2FnaFFBT294OHllNjd0Q2Y3bDYtT3BEaW5Gc2x1YThiY2VKcm9aSjFxRm9xSWJSRmlwY0h1dW44TzFEc0NmMng0b29rNzhpWUxzNVJKd3VURDNxQ01DWnlicVBQczdsNC12VmstbVhCV0ZFd2tON0dCLVFNYVZYbHItM1NUd2NUQ1lrall5X19sSlhnQVVxQnl3V0l6QlRBMFl1RFVWdkJvRGZPTzVBb1JRMjFtZ1lpaUFkV0dfVzJkMF8tNmp5WHVwTUxNNTF6YnpYR1JqcEtIUXZkVHA1QWIwbzdaSTdOemxocUZLWWp4NVUzVTd1b21WNFd3OU9fVVMwOURSbUdkQ1ZnOHhCMnRn?oc=5</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>派拉蒙與 WBD 合併：大衛·埃里森抱怨各州反壟斷訴訟的成本</t>
+          <t>PNR 警報：Hagens Berman 通知 Pentair plc（NYSE：PNR）投資者新證券集體訴訟的集體訴訟期限已延長，且首席原告截止日期即將到來</t>
         </is>
       </c>
       <c r="X15" s="4" t="inlineStr">
@@ -15872,28 +16308,28 @@
       </c>
       <c r="Y15" s="4" t="inlineStr">
         <is>
-          <t>ANTITRUST_INVESTIGATION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t>antitrust</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr">
         <is>
-          <t>a7d5bfc7abc64c2f89b22368f9e4e949</t>
+          <t>068e307f01664814a021033d7d9f7919</t>
         </is>
       </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t>2d86ee07e17f0b009cd76e34</t>
+          <t>369955a25f251f3fa2c0f456</t>
         </is>
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>7c7dddbb36f73ba60dc653c0</t>
+          <t>e383e1ec6967003c4dd50486</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr"/>
@@ -15925,7 +16361,7 @@
       <c r="BA15" s="4" t="inlineStr"/>
       <c r="BB15" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC15" s="4" t="inlineStr">
@@ -15955,7 +16391,7 @@
       </c>
       <c r="BL15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T15:43:17.016263+08:00</t>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
@@ -15972,22 +16408,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lennar Corporation Class A Common Stock</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T03:57:39+08:00</t>
+          <t>2026-08-15T05:48:00+08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Lennar Mortgage Data Breach Affects 60,526 Texans</t>
+          <t>General Motors files notice for 361 layoffs at Lansing assembly sites</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -15998,7 +16434,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>資料外洩</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16028,7 +16464,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>'-0.333</t>
+          <t>'-0.961</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -16037,53 +16473,53 @@
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>原始代號與公司名稱交叉核對</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFA4eGM3MHpxMTY1cEw5VFViYzlncGJaRkduVzBFeXEwM0oyaVR3UGE3VVNWNXhGSm5nNE91ZndNQS05a0hzZmNrRldXTVU1M0JySXN6ME1Fek5jbHZSaGZfVWxmQmdTdFR5bUU4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPc0x2QXl4OWNRQlE4M1hnc3ZSbTRCX1dyVVFYeERqdVctbHdueXZHMm4wZ2thamwyMVlQQi1KT3BZUXRoXzFpcWc1aV9BOVRZLTJRWXA3LXY0TjhwUnpDbTB2QXhhQWtWdExVUFJoZnQwU1ZYVTJ3Si00WDNXOG83d1RMVEE3aXVQcy1RcXRXUzNUeFRhU09CUVFHRmc3UU9icENaYXFTNDhpUEFwcVE?oc=5</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Claim Depot</t>
+          <t>MLive.com</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>Lennar 抵押貸款資料外洩影響 60,526 名德州人</t>
+          <t>通用汽車發布蘭辛組裝廠裁員 361 人的通知</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>DATA_BREACH</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>data breach</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>2b496ad463f54c6daf0411e83ac30753</t>
+          <t>e04f7e98362c42a0ad23362115af0b3a</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3f4be2ea1ff85d25253741b1</t>
+          <t>e2e6ef96b974fa9d958f7f1a</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>594eaa985b351c2648b735eb</t>
+          <t>75f4b793594615b4b14a5867</t>
         </is>
       </c>
       <c r="AE16" s="2" t="inlineStr"/>
@@ -16108,18 +16544,14 @@
       <c r="AT16" s="2" t="inlineStr"/>
       <c r="AU16" s="2" t="inlineStr"/>
       <c r="AV16" s="2" t="inlineStr"/>
-      <c r="AW16" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW16" s="2" t="inlineStr"/>
       <c r="AX16" s="2" t="inlineStr"/>
       <c r="AY16" s="2" t="inlineStr"/>
       <c r="AZ16" s="2" t="inlineStr"/>
       <c r="BA16" s="2" t="inlineStr"/>
       <c r="BB16" s="2" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="BC16" s="2" t="inlineStr">
@@ -16130,17 +16562,13 @@
       <c r="BD16" s="2" t="inlineStr"/>
       <c r="BE16" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF16" s="2" t="inlineStr"/>
       <c r="BG16" s="2" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
@@ -16158,192 +16586,192 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>General Motors</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-15T03:03:24+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>GM plans 350 layoffs in January at 2 Lansing sites, automaker confirms</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Paramount-WBD Merger: David Ellison Complains About Cost Of States' Antitrust Suit</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>'-0.944</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>'-0.929</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBhdUFlaWxXLVJIZDVPNnYzNGQ3ZDN5SW50N3kzOHNBR1AtM1pJbHFnN3RUczVEWWlGTDlidGhETXVVWjgzYVZjNDZOUkU1WWxLZm5lSVNVb2JmTjFRUVhrZmFPXzNtMmxSS0p2YmdjS2ZTR1g0?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>CBS News</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>汽車製造商證實，通用汽車計劃一月份在蘭辛的兩個工廠裁員 350 人</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>b5e41a37c7ef456ba43e158e3848720a</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>439d10c0ad4650e1d4257861</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>f0fdf05cdcafd109b09c51bd</t>
-        </is>
-      </c>
-      <c r="AE17" s="2" t="inlineStr"/>
-      <c r="AF17" s="2" t="inlineStr"/>
-      <c r="AG17" s="2" t="inlineStr"/>
-      <c r="AH17" s="2" t="inlineStr"/>
-      <c r="AI17" s="2" t="inlineStr"/>
-      <c r="AJ17" s="2" t="inlineStr"/>
-      <c r="AK17" s="2" t="inlineStr"/>
-      <c r="AL17" s="2" t="inlineStr"/>
-      <c r="AM17" s="2" t="inlineStr"/>
-      <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr">
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxON3Vua0xBT0RuclpJSjR1b2pvd2xqX003REkzdFB2TXU2WnlPRDNEQlQxN1RhWjJMelhiZ0J0SkVaM2ZYMWZWd1dqTDdudndkeTJ2YkUyT3pGcEZjOERwUDB4QklHUXpEbk5HSEZQUXJjMEhtLUY5amxQWk5vWjhWaW5MWHh0UFR1QktiY0dGSzZxWGllWDc0?oc=5</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>派拉蒙與 WBD 合併：大衛·埃里森抱怨各州反壟斷訴訟的成本</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>a7d5bfc7abc64c2f89b22368f9e4e949</t>
+        </is>
+      </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>2d86ee07e17f0b009cd76e34</t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>7c7dddbb36f73ba60dc653c0</t>
+        </is>
+      </c>
+      <c r="AE17" s="4" t="inlineStr"/>
+      <c r="AF17" s="4" t="inlineStr"/>
+      <c r="AG17" s="4" t="inlineStr"/>
+      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
+      <c r="AL17" s="4" t="inlineStr"/>
+      <c r="AM17" s="4" t="inlineStr"/>
+      <c r="AN17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP17" s="2" t="inlineStr"/>
-      <c r="AQ17" s="2" t="inlineStr"/>
-      <c r="AR17" s="2" t="inlineStr"/>
-      <c r="AS17" s="2" t="inlineStr"/>
-      <c r="AT17" s="2" t="inlineStr"/>
-      <c r="AU17" s="2" t="inlineStr"/>
-      <c r="AV17" s="2" t="inlineStr"/>
-      <c r="AW17" s="2" t="inlineStr"/>
-      <c r="AX17" s="2" t="inlineStr"/>
-      <c r="AY17" s="2" t="inlineStr"/>
-      <c r="AZ17" s="2" t="inlineStr"/>
-      <c r="BA17" s="2" t="inlineStr"/>
-      <c r="BB17" s="2" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BC17" s="2" t="inlineStr">
+      <c r="AP17" s="4" t="inlineStr"/>
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="4" t="inlineStr"/>
+      <c r="AS17" s="4" t="inlineStr"/>
+      <c r="AT17" s="4" t="inlineStr"/>
+      <c r="AU17" s="4" t="inlineStr"/>
+      <c r="AV17" s="4" t="inlineStr"/>
+      <c r="AW17" s="4" t="inlineStr"/>
+      <c r="AX17" s="4" t="inlineStr"/>
+      <c r="AY17" s="4" t="inlineStr"/>
+      <c r="AZ17" s="4" t="inlineStr"/>
+      <c r="BA17" s="4" t="inlineStr"/>
+      <c r="BB17" s="4" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="BC17" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD17" s="2" t="inlineStr"/>
-      <c r="BE17" s="2" t="inlineStr">
+      <c r="BD17" s="4" t="inlineStr"/>
+      <c r="BE17" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF17" s="2" t="inlineStr"/>
-      <c r="BG17" s="2" t="inlineStr">
+      <c r="BF17" s="4" t="inlineStr"/>
+      <c r="BG17" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
-      <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr">
+      <c r="BH17" s="4" t="inlineStr"/>
+      <c r="BI17" s="4" t="inlineStr"/>
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:54:08.043808+08:00</t>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
         </is>
       </c>
     </row>
@@ -16360,22 +16788,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>Lennar Corporation Class A Common Stock</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T01:57:29+08:00</t>
+          <t>2026-08-15T03:57:39+08:00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>GM layoffs hit Lansing plants for retooling</t>
+          <t>Lennar Mortgage Data Breach Affects 60,526 Texans</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -16386,7 +16814,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>資料外洩</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -16416,7 +16844,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>'-0.956</t>
+          <t>'-0.333</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -16425,53 +16853,53 @@
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>原始代號與公司名稱交叉核對</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPYXFMWkZuOHk1ZnBpYkJDdXlCSFVwSGZKcU9ZcUQ1NVZtZzFUaW01V3AyLUM3X0t1UnlVdVJCbVhBdUdjM2lDdV9EOXJGYXpNRXpacVBzNm8xLUoxYzNQUWQxMWRmNjFWS0ZROXdGR2RnX1JCMmlTaGNydmZ2R19FZWlIcmlmR1RjLXJ1RFdHX1V3cmY1b0tfbXBreUpZT2duN25aemV4eW44OURHMUdKaVlfZXk5MVpaSmpTTnp1aTdmZmNVYVkzSEJ1VUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFA4eGM3MHpxMTY1cEw5VFViYzlncGJaRkduVzBFeXEwM0oyaVR3UGE3VVNWNXhGSm5nNE91ZndNQS05a0hzZmNrRldXTVU1M0JySXN6ME1Fek5jbHZSaGZfVWxmQmdTdFR5bUU4?oc=5</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>The Detroit News</t>
+          <t>Claim Depot</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>通用汽車裁員對蘭辛工廠進行重組</t>
+          <t>Lennar 抵押貸款資料外洩影響 60,526 名德州人</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CYBER</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>DATA_BREACH</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>layoff；layoffs</t>
+          <t>data breach</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>f96a7d9569e6407c95ff266b36f3f29e</t>
+          <t>2b496ad463f54c6daf0411e83ac30753</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>abbf92acffae8d4fafa204f1</t>
+          <t>3f4be2ea1ff85d25253741b1</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>f5fcb7208bb5749889f76178</t>
+          <t>594eaa985b351c2648b735eb</t>
         </is>
       </c>
       <c r="AE18" s="2" t="inlineStr"/>
@@ -16496,14 +16924,18 @@
       <c r="AT18" s="2" t="inlineStr"/>
       <c r="AU18" s="2" t="inlineStr"/>
       <c r="AV18" s="2" t="inlineStr"/>
-      <c r="AW18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX18" s="2" t="inlineStr"/>
       <c r="AY18" s="2" t="inlineStr"/>
       <c r="AZ18" s="2" t="inlineStr"/>
       <c r="BA18" s="2" t="inlineStr"/>
       <c r="BB18" s="2" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="BC18" s="2" t="inlineStr">
@@ -16514,13 +16946,17 @@
       <c r="BD18" s="2" t="inlineStr"/>
       <c r="BE18" s="2" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF18" s="2" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG18" s="2" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
@@ -16560,12 +16996,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T01:57:00+08:00</t>
+          <t>2026-08-15T03:03:24+08:00</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>GM announces layoffs for Lansing Grand River plant retooling</t>
+          <t>GM plans 350 layoffs in January at 2 Lansing sites, automaker confirms</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -16606,7 +17042,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>'-0.943</t>
+          <t>'-0.944</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr"/>
@@ -16620,17 +17056,17 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQd2NQU1B5dnFUc256OU9RbllXRlNnOGtYTTlueFdPOEFxUEV5UmhQU25RalBJSmRlNmJFa2E5MTlmZXN4Nkh4ZjFBR05MZXBDYXRDcU5MWFRlNk1sNHZUTW0yVDh2eHh5UW82dXYtOFhjX3Q0bmF0Qy00a1ZKSE9ZU3FXUlBaNjIyaUxDaFdyckdYaGNxRVc2Qk1nLTc1MmRZQndzMU9SSExZbDczSEVuTXdMa2RRamJwWlVvWUgxM0dmX0NOaU5VUHpGdWxmT0FiajVkMS1xaThTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBhdUFlaWxXLVJIZDVPNnYzNGQ3ZDN5SW50N3kzOHNBR1AtM1pJbHFnN3RUczVEWWlGTDlidGhETXVVWjgzYVZjNDZOUkU1WWxLZm5lSVNVb2JmTjFRUVhrZmFPXzNtMmxSS0p2YmdjS2ZTR1g0?oc=5</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>The Detroit News</t>
+          <t>CBS News</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>通用汽車宣布因蘭辛大河工廠重組而裁員</t>
+          <t>汽車製造商證實，通用汽車計劃一月份在蘭辛的兩個工廠裁員 350 人</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -16651,17 +17087,17 @@
       <c r="AA19" s="2" t="inlineStr"/>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>290e67e44e1944a18e73713526f10802</t>
+          <t>b5e41a37c7ef456ba43e158e3848720a</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>d4929e30d6f04aa8426e97d4</t>
+          <t>439d10c0ad4650e1d4257861</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>f053cf659ea3bff6a6c26063</t>
+          <t>f0fdf05cdcafd109b09c51bd</t>
         </is>
       </c>
       <c r="AE19" s="2" t="inlineStr"/>
@@ -16728,391 +17164,973 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15T01:02:00+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise's settlement regarding $14B Juniper acquisition approved</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:57:29+08:00</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>GM layoffs hit Lansing plants for retooling</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>'-0.441</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>'-0.956</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPZE12MUtPNXBwUnpCdEcwM3AxSE5NRlNwSW8wS1BwdnFRdTZBZ0tKcHU1UGpVekt0VmFnSjU2TDBVY0djaXJZX1FrZFFOelUzQ0stQV9WZ1pncGhuR0t1OHlzQ2NBcHBuRThxVVZyNFJIZzd6WTRoel9XS0cyckRFT3NuSXFQX00xcWYySl9IRU9JRzlmTGdvNjI3NERNd3RURDZ5OFF3?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>The Business Journals</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr">
-        <is>
-          <t>惠普企業 (Hewlett Packard Enterprise) 關於 $14B 收購瞻博網路 (Juniper) 的和解協議已獲批准</t>
-        </is>
-      </c>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr">
-        <is>
-          <t>fa66ff9a193647a8956a03773fe52838</t>
-        </is>
-      </c>
-      <c r="AC20" s="4" t="inlineStr">
-        <is>
-          <t>1c5d6ce9a4bebc56f814d1d7</t>
-        </is>
-      </c>
-      <c r="AD20" s="4" t="inlineStr">
-        <is>
-          <t>dfee0c4216d9819c52d22141</t>
-        </is>
-      </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr"/>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr"/>
-      <c r="AI20" s="4" t="inlineStr"/>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPYXFMWkZuOHk1ZnBpYkJDdXlCSFVwSGZKcU9ZcUQ1NVZtZzFUaW01V3AyLUM3X0t1UnlVdVJCbVhBdUdjM2lDdV9EOXJGYXpNRXpacVBzNm8xLUoxYzNQUWQxMWRmNjFWS0ZROXdGR2RnX1JCMmlTaGNydmZ2R19FZWlIcmlmR1RjLXJ1RFdHX1V3cmY1b0tfbXBreUpZT2duN25aemV4eW44OURHMUdKaVlfZXk5MVpaSmpTTnp1aTdmZmNVYVkzSEJ1VUc?oc=5</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>The Detroit News</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>通用汽車裁員對蘭辛工廠進行重組</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>f96a7d9569e6407c95ff266b36f3f29e</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>abbf92acffae8d4fafa204f1</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>f5fcb7208bb5749889f76178</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AK20" s="2" t="inlineStr"/>
+      <c r="AL20" s="2" t="inlineStr"/>
+      <c r="AM20" s="2" t="inlineStr"/>
+      <c r="AN20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP20" s="4" t="inlineStr"/>
-      <c r="AQ20" s="4" t="inlineStr"/>
-      <c r="AR20" s="4" t="inlineStr"/>
-      <c r="AS20" s="4" t="inlineStr"/>
-      <c r="AT20" s="4" t="inlineStr"/>
-      <c r="AU20" s="4" t="inlineStr"/>
-      <c r="AV20" s="4" t="inlineStr"/>
-      <c r="AW20" s="4" t="inlineStr"/>
-      <c r="AX20" s="4" t="inlineStr"/>
-      <c r="AY20" s="4" t="inlineStr"/>
-      <c r="AZ20" s="4" t="inlineStr"/>
-      <c r="BA20" s="4" t="inlineStr"/>
-      <c r="BB20" s="4" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="BC20" s="4" t="inlineStr">
+      <c r="AP20" s="2" t="inlineStr"/>
+      <c r="AQ20" s="2" t="inlineStr"/>
+      <c r="AR20" s="2" t="inlineStr"/>
+      <c r="AS20" s="2" t="inlineStr"/>
+      <c r="AT20" s="2" t="inlineStr"/>
+      <c r="AU20" s="2" t="inlineStr"/>
+      <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" s="2" t="inlineStr"/>
+      <c r="AX20" s="2" t="inlineStr"/>
+      <c r="AY20" s="2" t="inlineStr"/>
+      <c r="AZ20" s="2" t="inlineStr"/>
+      <c r="BA20" s="2" t="inlineStr"/>
+      <c r="BB20" s="2" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="BC20" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="4" t="inlineStr"/>
-      <c r="BE20" s="4" t="inlineStr">
+      <c r="BD20" s="2" t="inlineStr"/>
+      <c r="BE20" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF20" s="4" t="inlineStr"/>
-      <c r="BG20" s="4" t="inlineStr">
+      <c r="BF20" s="2" t="inlineStr"/>
+      <c r="BG20" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH20" s="4" t="inlineStr"/>
-      <c r="BI20" s="4" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ20" s="4" t="inlineStr"/>
-      <c r="BK20" s="4" t="inlineStr">
+      <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>GM announces layoffs for Lansing Grand River plant retooling</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>'-0.943</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQd2NQU1B5dnFUc256OU9RbllXRlNnOGtYTTlueFdPOEFxUEV5UmhQU25RalBJSmRlNmJFa2E5MTlmZXN4Nkh4ZjFBR05MZXBDYXRDcU5MWFRlNk1sNHZUTW0yVDh2eHh5UW82dXYtOFhjX3Q0bmF0Qy00a1ZKSE9ZU3FXUlBaNjIyaUxDaFdyckdYaGNxRVc2Qk1nLTc1MmRZQndzMU9SSExZbDczSEVuTXdMa2RRamJwWlVvWUgxM0dmX0NOaU5VUHpGdWxmT0FiajVkMS1xaThTQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>The Detroit News</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>通用汽車宣布因蘭辛大河工廠重組而裁員</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>290e67e44e1944a18e73713526f10802</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>d4929e30d6f04aa8426e97d4</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>f053cf659ea3bff6a6c26063</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+      <c r="AK21" s="2" t="inlineStr"/>
+      <c r="AL21" s="2" t="inlineStr"/>
+      <c r="AM21" s="2" t="inlineStr"/>
+      <c r="AN21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP21" s="2" t="inlineStr"/>
+      <c r="AQ21" s="2" t="inlineStr"/>
+      <c r="AR21" s="2" t="inlineStr"/>
+      <c r="AS21" s="2" t="inlineStr"/>
+      <c r="AT21" s="2" t="inlineStr"/>
+      <c r="AU21" s="2" t="inlineStr"/>
+      <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" s="2" t="inlineStr"/>
+      <c r="AX21" s="2" t="inlineStr"/>
+      <c r="AY21" s="2" t="inlineStr"/>
+      <c r="AZ21" s="2" t="inlineStr"/>
+      <c r="BA21" s="2" t="inlineStr"/>
+      <c r="BB21" s="2" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="BC21" s="2" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD21" s="2" t="inlineStr"/>
+      <c r="BE21" s="2" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF21" s="2" t="inlineStr"/>
+      <c r="BG21" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TSN</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Tyson Foods, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:43:58+08:00</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Tyson Foods beef plant closures come as severe drought makes U.S. cattle shortages worse</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>工廠停工</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>'-0.961</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNSG1OMlVnREdUa2ljMGpjQV9SS01xWGI2ZE41WUZpNnU5SnBLMGpzOF90cGhxQTRZTGFaUDhWY2djNVQ5RW9lWTFjdDhGa1dJQVNfdmtNWnBUOUp5YmJaNWpVRXR5Mkw5eWRKNVN6Q1hfODZnd1pKdm42ZHdsZ09Kek92VFBXWEhNR0lhMkFwU3N5a3dWZy1jUEV1UmV6STdVOGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Fast Company</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>嚴重乾旱導緻美國牛短缺加劇，泰森食品牛肉工廠關閉</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>FACTORY_SHUTDOWN</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>drought</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>c2d0ad76fd1848128ca6738d97473d86</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>d6addd8557ffea972afec449</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>9dc3fc8a1dd81c971025377c</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr"/>
+      <c r="AL22" s="2" t="inlineStr"/>
+      <c r="AM22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP22" s="2" t="inlineStr"/>
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="inlineStr"/>
+      <c r="AS22" s="2" t="inlineStr"/>
+      <c r="AT22" s="2" t="inlineStr"/>
+      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr"/>
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr">
+        <is>
+          <t>TSN</t>
+        </is>
+      </c>
+      <c r="BC22" s="2" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD22" s="2" t="inlineStr"/>
+      <c r="BE22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG22" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:02:00+08:00</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise's settlement regarding $14B Juniper acquisition approved</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>'-0.441</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPZE12MUtPNXBwUnpCdEcwM3AxSE5NRlNwSW8wS1BwdnFRdTZBZ0tKcHU1UGpVekt0VmFnSjU2TDBVY0djaXJZX1FrZFFOelUzQ0stQV9WZ1pncGhuR0t1OHlzQ2NBcHBuRThxVVZyNFJIZzd6WTRoel9XS0cyckRFT3NuSXFQX00xcWYySl9IRU9JRzlmTGdvNjI3NERNd3RURDZ5OFF3?oc=5</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>The Business Journals</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>惠普企業 (Hewlett Packard Enterprise) 關於 $14B 收購瞻博網路 (Juniper) 的和解協議已獲批准</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>fa66ff9a193647a8956a03773fe52838</t>
+        </is>
+      </c>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>1c5d6ce9a4bebc56f814d1d7</t>
+        </is>
+      </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>dfee0c4216d9819c52d22141</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="inlineStr"/>
+      <c r="AF23" s="4" t="inlineStr"/>
+      <c r="AG23" s="4" t="inlineStr"/>
+      <c r="AH23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="inlineStr"/>
+      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr"/>
+      <c r="AL23" s="4" t="inlineStr"/>
+      <c r="AM23" s="4" t="inlineStr"/>
+      <c r="AN23" s="4" t="inlineStr"/>
+      <c r="AO23" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP23" s="4" t="inlineStr"/>
+      <c r="AQ23" s="4" t="inlineStr"/>
+      <c r="AR23" s="4" t="inlineStr"/>
+      <c r="AS23" s="4" t="inlineStr"/>
+      <c r="AT23" s="4" t="inlineStr"/>
+      <c r="AU23" s="4" t="inlineStr"/>
+      <c r="AV23" s="4" t="inlineStr"/>
+      <c r="AW23" s="4" t="inlineStr"/>
+      <c r="AX23" s="4" t="inlineStr"/>
+      <c r="AY23" s="4" t="inlineStr"/>
+      <c r="AZ23" s="4" t="inlineStr"/>
+      <c r="BA23" s="4" t="inlineStr"/>
+      <c r="BB23" s="4" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="BC23" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD23" s="4" t="inlineStr"/>
+      <c r="BE23" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF23" s="4" t="inlineStr"/>
+      <c r="BG23" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH23" s="4" t="inlineStr"/>
+      <c r="BI23" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ23" s="4" t="inlineStr"/>
+      <c r="BK23" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Pentair</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>2026-08-15T00:05:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>EXPANDED CLASS PERIOD - Law Offices of Frank R. Cruz Encourages Pentair plc (PNR) Shareholders To Inquire About Securities Fraud Class Action</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>'-0.048</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="U24" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxPSmJWa09MbzhpTGRKN2JfaExKYlVoS2RWWUVweC10ZWZ6TkJLNnJlNjZkZ3c4cjR0MjdpUXdzLTBnbVJIM01vaUVqYlRvWFhaMnB1OEJmb2tIUkdRYU5XdmVGdlYzbC05LTRDQUt4Sk5VakdIUDVkR01yUkhUbTNHSHBwR010QkZyd1Zac25QWW9wbkpScV9XcE45eGlET0pYcS1KdUNXVGstSElxTHBaSnRnZm4tSnVMVHVKZ0VCTTlNNFhNNTlSVTJBRklTM01nVmdVMUpkTzdteUZadkJwWm40bE50VnJkaHZzTVdNd25leXE5RVAwRmQwY21maGlWTFYzWUNwODd6SkdqNlVvd2ktZmp2eXd4bm1UNFNxVHROUQ?oc=5</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>Business Wire</t>
         </is>
       </c>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="W24" s="4" t="inlineStr">
         <is>
           <t>延長集體訴訟期限 - Frank R. Cruz 律師事務所鼓勵 Pentair plc (PNR) 股東詢問有關證券詐欺集體訴訟的情況</t>
         </is>
       </c>
-      <c r="X21" s="4" t="inlineStr">
+      <c r="X24" s="4" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y21" s="4" t="inlineStr">
+      <c r="Y24" s="4" t="inlineStr">
         <is>
           <t>MAJOR_LITIGATION</t>
         </is>
       </c>
-      <c r="Z21" s="4" t="inlineStr">
+      <c r="Z24" s="4" t="inlineStr">
         <is>
           <t>class action</t>
         </is>
       </c>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr">
+      <c r="AA24" s="4" t="inlineStr"/>
+      <c r="AB24" s="4" t="inlineStr">
         <is>
           <t>40a91b47bd344836848eceab41eca967</t>
         </is>
       </c>
-      <c r="AC21" s="4" t="inlineStr">
+      <c r="AC24" s="4" t="inlineStr">
         <is>
           <t>8301ccddb88c291ef77e4cfa</t>
         </is>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AD24" s="4" t="inlineStr">
         <is>
           <t>1cf84168c856e441c1e85131</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr">
+      <c r="AE24" s="4" t="inlineStr"/>
+      <c r="AF24" s="4" t="inlineStr"/>
+      <c r="AG24" s="4" t="inlineStr"/>
+      <c r="AH24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="inlineStr"/>
+      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr"/>
+      <c r="AL24" s="4" t="inlineStr"/>
+      <c r="AM24" s="4" t="inlineStr"/>
+      <c r="AN24" s="4" t="inlineStr"/>
+      <c r="AO24" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr"/>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
+      <c r="AP24" s="4" t="inlineStr"/>
+      <c r="AQ24" s="4" t="inlineStr"/>
+      <c r="AR24" s="4" t="inlineStr"/>
+      <c r="AS24" s="4" t="inlineStr"/>
+      <c r="AT24" s="4" t="inlineStr"/>
+      <c r="AU24" s="4" t="inlineStr"/>
+      <c r="AV24" s="4" t="inlineStr"/>
+      <c r="AW24" s="4" t="inlineStr"/>
+      <c r="AX24" s="4" t="inlineStr"/>
+      <c r="AY24" s="4" t="inlineStr"/>
+      <c r="AZ24" s="4" t="inlineStr"/>
+      <c r="BA24" s="4" t="inlineStr"/>
+      <c r="BB24" s="4" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="BC21" s="4" t="inlineStr">
+      <c r="BC24" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
+      <c r="BD24" s="4" t="inlineStr"/>
+      <c r="BE24" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF21" s="4" t="inlineStr"/>
-      <c r="BG21" s="4" t="inlineStr">
+      <c r="BF24" s="4" t="inlineStr"/>
+      <c r="BG24" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH21" s="4" t="inlineStr"/>
-      <c r="BI21" s="4" t="inlineStr"/>
-      <c r="BJ21" s="4" t="inlineStr"/>
-      <c r="BK21" s="4" t="inlineStr">
+      <c r="BH24" s="4" t="inlineStr"/>
+      <c r="BI24" s="4" t="inlineStr"/>
+      <c r="BJ24" s="4" t="inlineStr"/>
+      <c r="BK24" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL21" s="4" t="inlineStr">
+      <c r="BL24" s="4" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL21"/>
+  <autoFilter ref="A1:BL24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
